--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-28).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-28).xlsx
@@ -912,36 +912,36 @@
   </si>
   <si>
     <t>214
-170</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>R$ 541.339,01</t>
-  </si>
-  <si>
-    <t>R$ 3.024,24
-R$ 3.081,45</t>
-  </si>
-  <si>
-    <t>3.0%
-4.6%</t>
-  </si>
-  <si>
-    <t>34.7</t>
-  </si>
-  <si>
-    <t>(1.6%)</t>
-  </si>
-  <si>
-    <t>3.9%</t>
-  </si>
-  <si>
-    <t>(40.8%)</t>
-  </si>
-  <si>
-    <t>4.6%</t>
+175</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>R$ 553.242,41</t>
+  </si>
+  <si>
+    <t>R$ 3.006,75
+R$ 3.061,43</t>
+  </si>
+  <si>
+    <t>3.2%
+4.8%</t>
+  </si>
+  <si>
+    <t>34.5</t>
+  </si>
+  <si>
+    <t>(1.4%)</t>
+  </si>
+  <si>
+    <t>4.4%</t>
+  </si>
+  <si>
+    <t>(40.1%)</t>
+  </si>
+  <si>
+    <t>4.7%</t>
   </si>
   <si>
     <t>0.0%</t>
@@ -953,13 +953,13 @@
     <t>76.7%</t>
   </si>
   <si>
-    <t>7.0%</t>
+    <t>6.9%</t>
   </si>
   <si>
     <t>4.6</t>
   </si>
   <si>
-    <t>6.3</t>
+    <t>6.2</t>
   </si>
   <si>
     <t>10.9</t>
@@ -968,10 +968,10 @@
     <t>17.6</t>
   </si>
   <si>
-    <t>77.8%</t>
-  </si>
-  <si>
-    <t>-R$ 17.018,83</t>
+    <t>77.9%</t>
+  </si>
+  <si>
+    <t>-R$ 17.360,33</t>
   </si>
   <si>
     <t>2.94</t>
@@ -3025,7 +3025,9 @@
       <c r="AB13" s="8">
         <v>5.7265159090909092</v>
       </c>
-      <c r="AC13" s="8"/>
+      <c r="AC13" s="8">
+        <v>10.810226999999999</v>
+      </c>
       <c r="AD13" s="8">
         <v>17.384073333333333</v>
       </c>
@@ -5922,7 +5924,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>44</v>
@@ -5958,25 +5960,59 @@
       <c t="s" r="N36" s="4">
         <v>52</v>
       </c>
-      <c r="O36" s="5"/>
-      <c r="P36" s="5"/>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="7"/>
-      <c r="S36" s="6"/>
-      <c r="T36" s="6"/>
-      <c r="U36" s="6"/>
-      <c r="V36" s="6"/>
-      <c r="W36" s="6"/>
-      <c r="X36" s="8"/>
-      <c r="Y36" s="6"/>
-      <c r="Z36" s="6"/>
-      <c r="AA36" s="8"/>
-      <c r="AB36" s="8"/>
+      <c r="O36" s="5">
+        <v>4667.3800000000001</v>
+      </c>
+      <c r="P36" s="5">
+        <v>4667.3800000000001</v>
+      </c>
+      <c r="Q36" s="6">
+        <v>1.6442880775942168</v>
+      </c>
+      <c r="R36" s="7">
+        <v>38</v>
+      </c>
+      <c r="S36" s="6">
+        <v>0.89999999999999991</v>
+      </c>
+      <c r="T36" s="6">
+        <v>0.34663194340293696</v>
+      </c>
+      <c r="U36" s="6">
+        <v>0.035110276000668468</v>
+      </c>
+      <c r="V36" s="6">
+        <v>0.057265960774567311</v>
+      </c>
+      <c r="W36" s="6">
+        <v>0.014674614023285014</v>
+      </c>
+      <c r="X36" s="8">
+        <v>24.830769230769231</v>
+      </c>
+      <c r="Y36" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z36" s="6">
+        <v>0.038461538461538464</v>
+      </c>
+      <c r="AA36" s="8">
+        <v>5.2092583333333335</v>
+      </c>
+      <c r="AB36" s="8">
+        <v>4.3871807692307687</v>
+      </c>
       <c r="AC36" s="8"/>
-      <c r="AD36" s="8"/>
-      <c r="AE36" s="6"/>
+      <c r="AD36" s="8">
+        <v>16.489742307692307</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>0.84615384615384615</v>
+      </c>
       <c r="AF36" s="9"/>
-      <c r="AG36" s="5"/>
+      <c r="AG36" s="5">
+        <v>0</v>
+      </c>
       <c r="AH36" s="10">
         <v>4</v>
       </c>
@@ -6672,7 +6708,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>44</v>
@@ -6708,25 +6744,61 @@
       <c t="s" r="N42" s="4">
         <v>52</v>
       </c>
-      <c r="O42" s="5"/>
-      <c r="P42" s="5"/>
-      <c r="Q42" s="6"/>
-      <c r="R42" s="7"/>
-      <c r="S42" s="6"/>
-      <c r="T42" s="6"/>
-      <c r="U42" s="6"/>
-      <c r="V42" s="6"/>
-      <c r="W42" s="6"/>
-      <c r="X42" s="8"/>
-      <c r="Y42" s="6"/>
-      <c r="Z42" s="6"/>
-      <c r="AA42" s="8"/>
-      <c r="AB42" s="8"/>
-      <c r="AC42" s="8"/>
-      <c r="AD42" s="8"/>
-      <c r="AE42" s="6"/>
+      <c r="O42" s="5">
+        <v>2082.0900000000001</v>
+      </c>
+      <c r="P42" s="5">
+        <v>2082.0900000000001</v>
+      </c>
+      <c r="Q42" s="6">
+        <v>0.14701167345184918</v>
+      </c>
+      <c r="R42" s="7">
+        <v>29</v>
+      </c>
+      <c r="S42" s="6">
+        <v>0.38095238095238093</v>
+      </c>
+      <c r="T42" s="6">
+        <v>0.093599700301139718</v>
+      </c>
+      <c r="U42" s="6">
+        <v>-0.18098977469753946</v>
+      </c>
+      <c r="V42" s="6">
+        <v>0.084887781027717338</v>
+      </c>
+      <c r="W42" s="6">
+        <v>0.019688870317805664</v>
+      </c>
+      <c r="X42" s="8">
+        <v>21.94920476190476</v>
+      </c>
+      <c r="Y42" s="6">
+        <v>0.80952380952380953</v>
+      </c>
+      <c r="Z42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="8">
+        <v>4.5047607142857142</v>
+      </c>
+      <c r="AB42" s="8">
+        <v>5.5214285714285714</v>
+      </c>
+      <c r="AC42" s="8">
+        <v>10.210316000000001</v>
+      </c>
+      <c r="AD42" s="8">
+        <v>17.159523809523812</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>0.90476190476190477</v>
+      </c>
       <c r="AF42" s="9"/>
-      <c r="AG42" s="5"/>
+      <c r="AG42" s="5">
+        <v>0</v>
+      </c>
       <c r="AH42" s="10">
         <v>3</v>
       </c>
@@ -7807,7 +7879,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>44</v>
@@ -7843,25 +7915,59 @@
       <c t="s" r="N51" s="4">
         <v>52</v>
       </c>
-      <c r="O51" s="5"/>
-      <c r="P51" s="5"/>
-      <c r="Q51" s="6"/>
-      <c r="R51" s="7"/>
-      <c r="S51" s="6"/>
-      <c r="T51" s="6"/>
-      <c r="U51" s="6"/>
-      <c r="V51" s="6"/>
-      <c r="W51" s="6"/>
-      <c r="X51" s="8"/>
-      <c r="Y51" s="6"/>
-      <c r="Z51" s="6"/>
-      <c r="AA51" s="8"/>
-      <c r="AB51" s="8"/>
+      <c r="O51" s="5">
+        <v>481.69999999999999</v>
+      </c>
+      <c r="P51" s="5">
+        <v>481.69999999999999</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>-0.42612404393719172</v>
+      </c>
+      <c r="R51" s="7">
+        <v>4</v>
+      </c>
+      <c r="S51" s="6">
+        <v>-0.55555555555555558</v>
+      </c>
+      <c r="T51" s="6">
+        <v>0</v>
+      </c>
+      <c r="U51" s="6">
+        <v>-0.2845131824787212</v>
+      </c>
+      <c r="V51" s="6">
+        <v>0.086686734482042768</v>
+      </c>
+      <c r="W51" s="6">
+        <v>-0.17905958065185801</v>
+      </c>
+      <c r="X51" s="8">
+        <v>31.283300000000001</v>
+      </c>
+      <c r="Y51" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="8">
+        <v>5.6458250000000003</v>
+      </c>
+      <c r="AB51" s="8">
+        <v>6.1666999999999996</v>
+      </c>
       <c r="AC51" s="8"/>
-      <c r="AD51" s="8"/>
-      <c r="AE51" s="6"/>
+      <c r="AD51" s="8">
+        <v>24.916699999999999</v>
+      </c>
+      <c r="AE51" s="6">
+        <v>0</v>
+      </c>
       <c r="AF51" s="9"/>
-      <c r="AG51" s="5"/>
+      <c r="AG51" s="5">
+        <v>0</v>
+      </c>
       <c r="AH51" s="10">
         <v>2</v>
       </c>
@@ -8734,7 +8840,9 @@
       <c r="Z58" s="6"/>
       <c r="AA58" s="8"/>
       <c r="AB58" s="8"/>
-      <c r="AC58" s="8"/>
+      <c r="AC58" s="8">
+        <v>9.6245600000000007</v>
+      </c>
       <c r="AD58" s="8"/>
       <c r="AE58" s="6"/>
       <c r="AF58" s="9"/>
@@ -10964,7 +11072,9 @@
       <c r="AB76" s="8">
         <v>4.1523138888888891</v>
       </c>
-      <c r="AC76" s="8"/>
+      <c r="AC76" s="8">
+        <v>8.3662019999999995</v>
+      </c>
       <c r="AD76" s="8">
         <v>17.313425000000002</v>
       </c>
@@ -14164,7 +14274,7 @@
         <v>19719</v>
       </c>
       <c r="B102" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C102" s="4">
         <v>44</v>
@@ -14200,25 +14310,61 @@
       <c t="s" r="N102" s="4">
         <v>52</v>
       </c>
-      <c r="O102" s="5"/>
-      <c r="P102" s="5"/>
-      <c r="Q102" s="6"/>
-      <c r="R102" s="7"/>
-      <c r="S102" s="6"/>
-      <c r="T102" s="6"/>
-      <c r="U102" s="6"/>
-      <c r="V102" s="6"/>
-      <c r="W102" s="6"/>
-      <c r="X102" s="8"/>
-      <c r="Y102" s="6"/>
-      <c r="Z102" s="6"/>
-      <c r="AA102" s="8"/>
-      <c r="AB102" s="8"/>
-      <c r="AC102" s="8"/>
-      <c r="AD102" s="8"/>
-      <c r="AE102" s="6"/>
+      <c r="O102" s="5">
+        <v>1815.3</v>
+      </c>
+      <c r="P102" s="5">
+        <v>1815.3</v>
+      </c>
+      <c r="Q102" s="6">
+        <v>-0.42402147426134629</v>
+      </c>
+      <c r="R102" s="7">
+        <v>23</v>
+      </c>
+      <c r="S102" s="6">
+        <v>-0.2068965517241379</v>
+      </c>
+      <c r="T102" s="6">
+        <v>0</v>
+      </c>
+      <c r="U102" s="6">
+        <v>-0.33165867900622487</v>
+      </c>
+      <c r="V102" s="6">
+        <v>0.11032639233184598</v>
+      </c>
+      <c r="W102" s="6">
+        <v>0.0673748140803173</v>
+      </c>
+      <c r="X102" s="8">
+        <v>26.36470588235294</v>
+      </c>
+      <c r="Y102" s="6">
+        <v>0.41176470588235292</v>
+      </c>
+      <c r="Z102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="8">
+        <v>4.8007590909090903</v>
+      </c>
+      <c r="AB102" s="8">
+        <v>6.1270812499999998</v>
+      </c>
+      <c r="AC102" s="8">
+        <v>11.070220000000001</v>
+      </c>
+      <c r="AD102" s="8">
+        <v>17.290194117647058</v>
+      </c>
+      <c r="AE102" s="6">
+        <v>0.70588235294117652</v>
+      </c>
       <c r="AF102" s="9"/>
-      <c r="AG102" s="5"/>
+      <c r="AG102" s="5">
+        <v>0</v>
+      </c>
       <c r="AH102" s="10">
         <v>2</v>
       </c>
@@ -17040,7 +17186,7 @@
         <v>0.055520139504302332</v>
       </c>
       <c r="W125" s="6">
-        <v>-0.0030878667467101185</v>
+        <v>-0.0015203491419151346</v>
       </c>
       <c r="X125" s="8">
         <v>27.665217391304346</v>
@@ -21433,7 +21579,7 @@
         <v>0.15359241641827343</v>
       </c>
       <c r="W160" s="6">
-        <v>0.048933558819703286</v>
+        <v>0.046303512949440906</v>
       </c>
       <c r="X160" s="8">
         <v>37.657692307692308</v>
@@ -25837,7 +25983,7 @@
         <v>19944</v>
       </c>
       <c r="B195" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C195" s="4">
         <v>44</v>
@@ -25873,25 +26019,59 @@
       <c t="s" r="N195" s="4">
         <v>52</v>
       </c>
-      <c r="O195" s="5"/>
-      <c r="P195" s="5"/>
-      <c r="Q195" s="6"/>
-      <c r="R195" s="7"/>
-      <c r="S195" s="6"/>
-      <c r="T195" s="6"/>
-      <c r="U195" s="6"/>
-      <c r="V195" s="6"/>
-      <c r="W195" s="6"/>
-      <c r="X195" s="8"/>
-      <c r="Y195" s="6"/>
-      <c r="Z195" s="6"/>
-      <c r="AA195" s="8"/>
-      <c r="AB195" s="8"/>
+      <c r="O195" s="5">
+        <v>2856.9299999999998</v>
+      </c>
+      <c r="P195" s="5">
+        <v>2856.9299999999998</v>
+      </c>
+      <c r="Q195" s="6">
+        <v>-0.045733754196102039</v>
+      </c>
+      <c r="R195" s="7">
+        <v>37</v>
+      </c>
+      <c r="S195" s="6">
+        <v>-0.15909090909090906</v>
+      </c>
+      <c r="T195" s="6">
+        <v>0.35397374104370777</v>
+      </c>
+      <c r="U195" s="6">
+        <v>0.044984721361741455</v>
+      </c>
+      <c r="V195" s="6">
+        <v>0.042020455523936531</v>
+      </c>
+      <c r="W195" s="6">
+        <v>0.0039831217425698217</v>
+      </c>
+      <c r="X195" s="8">
+        <v>22.104627777777779</v>
+      </c>
+      <c r="Y195" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="Z195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA195" s="8">
+        <v>4.0779411764705884</v>
+      </c>
+      <c r="AB195" s="8">
+        <v>4.2666666666666666</v>
+      </c>
       <c r="AC195" s="8"/>
-      <c r="AD195" s="8"/>
-      <c r="AE195" s="6"/>
+      <c r="AD195" s="8">
+        <v>15.332405555555555</v>
+      </c>
+      <c r="AE195" s="6">
+        <v>0.94444444444444442</v>
+      </c>
       <c r="AF195" s="9"/>
-      <c r="AG195" s="5"/>
+      <c r="AG195" s="5">
+        <v>-341.5</v>
+      </c>
       <c r="AH195" s="10">
         <v>2</v>
       </c>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-28).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-28).xlsx
@@ -912,48 +912,45 @@
   </si>
   <si>
     <t>214
-175</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>R$ 553.242,41</t>
-  </si>
-  <si>
-    <t>R$ 3.006,75
-R$ 3.061,43</t>
-  </si>
-  <si>
-    <t>3.2%
-4.8%</t>
+177</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>R$ 559.801,47</t>
+  </si>
+  <si>
+    <t>R$ 3.009,69
+R$ 3.063,89</t>
+  </si>
+  <si>
+    <t>3.5%
+5.0%</t>
   </si>
   <si>
     <t>34.5</t>
   </si>
   <si>
-    <t>(1.4%)</t>
-  </si>
-  <si>
-    <t>4.4%</t>
-  </si>
-  <si>
-    <t>(40.1%)</t>
+    <t>(1.3%)</t>
   </si>
   <si>
     <t>4.7%</t>
   </si>
   <si>
+    <t>(39.6%)</t>
+  </si>
+  <si>
     <t>0.0%</t>
   </si>
   <si>
     <t>25.2</t>
   </si>
   <si>
-    <t>76.7%</t>
-  </si>
-  <si>
-    <t>6.9%</t>
+    <t>77.0%</t>
+  </si>
+  <si>
+    <t>6.8%</t>
   </si>
   <si>
     <t>4.6</t>
@@ -962,13 +959,13 @@
     <t>6.2</t>
   </si>
   <si>
-    <t>10.9</t>
+    <t>10.8</t>
   </si>
   <si>
     <t>17.6</t>
   </si>
   <si>
-    <t>77.9%</t>
+    <t>78.2%</t>
   </si>
   <si>
     <t>-R$ 17.360,33</t>
@@ -2066,7 +2063,7 @@
         <v>19507</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>44</v>
@@ -2102,25 +2099,61 @@
       <c t="s" r="N6" s="4">
         <v>52</v>
       </c>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="7"/>
-      <c r="S6" s="6"/>
-      <c r="T6" s="6"/>
-      <c r="U6" s="6"/>
-      <c r="V6" s="6"/>
-      <c r="W6" s="6"/>
-      <c r="X6" s="8"/>
-      <c r="Y6" s="6"/>
-      <c r="Z6" s="6"/>
-      <c r="AA6" s="8"/>
-      <c r="AB6" s="8"/>
-      <c r="AC6" s="8"/>
-      <c r="AD6" s="8"/>
-      <c r="AE6" s="6"/>
+      <c r="O6" s="5">
+        <v>3844.6100000000001</v>
+      </c>
+      <c r="P6" s="5">
+        <v>3844.6100000000001</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>0.12762025992157189</v>
+      </c>
+      <c r="R6" s="7">
+        <v>41</v>
+      </c>
+      <c r="S6" s="6">
+        <v>0</v>
+      </c>
+      <c r="T6" s="6">
+        <v>0.29984209061517292</v>
+      </c>
+      <c r="U6" s="6">
+        <v>-0.015760792382062159</v>
+      </c>
+      <c r="V6" s="6">
+        <v>0.036732074254605791</v>
+      </c>
+      <c r="W6" s="6">
+        <v>-0.0029390497345634539</v>
+      </c>
+      <c r="X6" s="8">
+        <v>21.465685294117648</v>
+      </c>
+      <c r="Y6" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="8">
+        <v>5.002031707317073</v>
+      </c>
+      <c r="AB6" s="8">
+        <v>2.8446088235294118</v>
+      </c>
+      <c r="AC6" s="8">
+        <v>7.9725479999999997</v>
+      </c>
+      <c r="AD6" s="8">
+        <v>14.933332352941177</v>
+      </c>
+      <c r="AE6" s="6">
+        <v>0.97058823529411764</v>
+      </c>
       <c r="AF6" s="9"/>
-      <c r="AG6" s="5"/>
+      <c r="AG6" s="5">
+        <v>0</v>
+      </c>
       <c r="AH6" s="10">
         <v>5</v>
       </c>
@@ -6002,7 +6035,9 @@
       <c r="AB36" s="8">
         <v>4.3871807692307687</v>
       </c>
-      <c r="AC36" s="8"/>
+      <c r="AC36" s="8">
+        <v>9.5352549999999994</v>
+      </c>
       <c r="AD36" s="8">
         <v>16.489742307692307</v>
       </c>
@@ -7957,7 +7992,9 @@
       <c r="AB51" s="8">
         <v>6.1666999999999996</v>
       </c>
-      <c r="AC51" s="8"/>
+      <c r="AC51" s="8">
+        <v>18.133331999999999</v>
+      </c>
       <c r="AD51" s="8">
         <v>24.916699999999999</v>
       </c>
@@ -12583,7 +12620,7 @@
         <v>0.04413356098758308</v>
       </c>
       <c r="W88" s="6">
-        <v>0.0027014923123628745</v>
+        <v>0.016858112981674979</v>
       </c>
       <c r="X88" s="8">
         <v>25.586363636363636</v>
@@ -12807,7 +12844,7 @@
         <v>0.098374282083362061</v>
       </c>
       <c r="W90" s="6">
-        <v>0.065793427183796507</v>
+        <v>0.069032056270872541</v>
       </c>
       <c r="X90" s="8">
         <v>40.63055555555556</v>
@@ -21296,7 +21333,7 @@
         <v>19859</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C158" s="4">
         <v>44</v>
@@ -21332,25 +21369,61 @@
       <c t="s" r="N158" s="4">
         <v>52</v>
       </c>
-      <c r="O158" s="5"/>
-      <c r="P158" s="5"/>
-      <c r="Q158" s="6"/>
-      <c r="R158" s="7"/>
-      <c r="S158" s="6"/>
-      <c r="T158" s="6"/>
-      <c r="U158" s="6"/>
-      <c r="V158" s="6"/>
-      <c r="W158" s="6"/>
-      <c r="X158" s="8"/>
-      <c r="Y158" s="6"/>
-      <c r="Z158" s="6"/>
-      <c r="AA158" s="8"/>
-      <c r="AB158" s="8"/>
-      <c r="AC158" s="8"/>
-      <c r="AD158" s="8"/>
-      <c r="AE158" s="6"/>
+      <c r="O158" s="5">
+        <v>2714.4499999999998</v>
+      </c>
+      <c r="P158" s="5">
+        <v>2714.4499999999998</v>
+      </c>
+      <c r="Q158" s="6">
+        <v>0.73380812468063361</v>
+      </c>
+      <c r="R158" s="7">
+        <v>25</v>
+      </c>
+      <c r="S158" s="6">
+        <v>0.5625</v>
+      </c>
+      <c r="T158" s="6">
+        <v>0.30290659249571739</v>
+      </c>
+      <c r="U158" s="6">
+        <v>0.017368085615870617</v>
+      </c>
+      <c r="V158" s="6">
+        <v>0.039575604634456342</v>
+      </c>
+      <c r="W158" s="6">
+        <v>-0.034015730626830484</v>
+      </c>
+      <c r="X158" s="8">
+        <v>24.371665</v>
+      </c>
+      <c r="Y158" s="6">
+        <v>0.90000000000000002</v>
+      </c>
+      <c r="Z158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA158" s="8">
+        <v>4.6724346153846152</v>
+      </c>
+      <c r="AB158" s="8">
+        <v>3.206142105263158</v>
+      </c>
+      <c r="AC158" s="8">
+        <v>8.0871999999999993</v>
+      </c>
+      <c r="AD158" s="8">
+        <v>14.925835000000001</v>
+      </c>
+      <c r="AE158" s="6">
+        <v>0.90000000000000002</v>
+      </c>
       <c r="AF158" s="9"/>
-      <c r="AG158" s="5"/>
+      <c r="AG158" s="5">
+        <v>0</v>
+      </c>
       <c r="AH158" s="10">
         <v>2</v>
       </c>
@@ -28438,44 +28511,44 @@
         <v>308</v>
       </c>
       <c t="s" r="V216" s="14">
+        <v>307</v>
+      </c>
+      <c t="s" r="W216" s="14">
         <v>309</v>
       </c>
-      <c t="s" r="W216" s="14">
+      <c t="s" r="X216" s="14">
         <v>310</v>
       </c>
-      <c t="s" r="X216" s="14">
+      <c t="s" r="Y216" s="14">
         <v>311</v>
       </c>
-      <c t="s" r="Y216" s="14">
+      <c t="s" r="Z216" s="14">
         <v>312</v>
       </c>
-      <c t="s" r="Z216" s="14">
+      <c t="s" r="AA216" s="14">
         <v>313</v>
       </c>
-      <c t="s" r="AA216" s="14">
+      <c t="s" r="AB216" s="14">
         <v>314</v>
       </c>
-      <c t="s" r="AB216" s="14">
+      <c t="s" r="AC216" s="14">
         <v>315</v>
       </c>
-      <c t="s" r="AC216" s="14">
+      <c t="s" r="AD216" s="14">
         <v>316</v>
       </c>
-      <c t="s" r="AD216" s="14">
+      <c t="s" r="AE216" s="14">
         <v>317</v>
-      </c>
-      <c t="s" r="AE216" s="14">
-        <v>318</v>
       </c>
       <c r="AF216" s="14"/>
       <c t="s" r="AG216" s="14">
+        <v>318</v>
+      </c>
+      <c t="s" r="AH216" s="14">
         <v>319</v>
       </c>
-      <c t="s" r="AH216" s="14">
+      <c t="s" r="AI216" s="14">
         <v>320</v>
-      </c>
-      <c t="s" r="AI216" s="14">
-        <v>321</v>
       </c>
       <c r="AJ216" s="15"/>
       <c t="s" r="AK216" s="15">
@@ -28485,10 +28558,10 @@
         <v>52</v>
       </c>
       <c t="s" r="AM216" s="14">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c t="s" r="AN216" s="14">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AO216" s="15"/>
       <c r="AP216" s="15"/>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-28).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-28).xlsx
@@ -911,46 +911,49 @@
     <t>GUIMARAES FRAGA,MARESSA</t>
   </si>
   <si>
-    <t>214
-177</t>
+    <t>DE LOURDES RAMOS,MARIA</t>
+  </si>
+  <si>
+    <t>215
+178</t>
   </si>
   <si>
     <t>26</t>
   </si>
   <si>
-    <t>R$ 559.801,47</t>
-  </si>
-  <si>
-    <t>R$ 3.009,69
-R$ 3.063,89</t>
-  </si>
-  <si>
-    <t>3.5%
-5.0%</t>
-  </si>
-  <si>
-    <t>34.5</t>
-  </si>
-  <si>
-    <t>(1.3%)</t>
+    <t>R$ 560.890,63</t>
+  </si>
+  <si>
+    <t>R$ 2.999,42
+R$ 3.052,80</t>
+  </si>
+  <si>
+    <t>3.6%
+5.1%</t>
+  </si>
+  <si>
+    <t>34.4</t>
+  </si>
+  <si>
+    <t>(1.2%)</t>
   </si>
   <si>
     <t>4.7%</t>
   </si>
   <si>
-    <t>(39.6%)</t>
-  </si>
-  <si>
-    <t>0.0%</t>
-  </si>
-  <si>
-    <t>25.2</t>
+    <t>(39.5%)</t>
+  </si>
+  <si>
+    <t>0.1%</t>
+  </si>
+  <si>
+    <t>25.1</t>
   </si>
   <si>
     <t>77.0%</t>
   </si>
   <si>
-    <t>6.8%</t>
+    <t>6.7%</t>
   </si>
   <si>
     <t>4.6</t>
@@ -962,7 +965,7 @@
     <t>10.8</t>
   </si>
   <si>
-    <t>17.6</t>
+    <t>17.5</t>
   </si>
   <si>
     <t>78.2%</t>
@@ -5743,10 +5746,10 @@
         <v>0.58000000000000007</v>
       </c>
       <c r="T34" s="6">
-        <v>0.11281842317215046</v>
+        <v>0.10556760035398582</v>
       </c>
       <c r="U34" s="6">
-        <v>-0.22917563066153587</v>
+        <v>-0.23642645347970051</v>
       </c>
       <c r="V34" s="6">
         <v>0.10118714514412991</v>
@@ -16073,7 +16076,9 @@
       <c r="Z116" s="6"/>
       <c r="AA116" s="8"/>
       <c r="AB116" s="8"/>
-      <c r="AC116" s="8"/>
+      <c r="AC116" s="8">
+        <v>15.558012</v>
+      </c>
       <c r="AD116" s="8"/>
       <c r="AE116" s="6"/>
       <c r="AF116" s="9"/>
@@ -19214,7 +19219,7 @@
         <v>19793</v>
       </c>
       <c r="B141" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C141" s="4">
         <v>44</v>
@@ -19250,25 +19255,61 @@
       <c t="s" r="N141" s="4">
         <v>52</v>
       </c>
-      <c r="O141" s="5"/>
-      <c r="P141" s="5"/>
-      <c r="Q141" s="6"/>
-      <c r="R141" s="7"/>
-      <c r="S141" s="6"/>
-      <c r="T141" s="6"/>
-      <c r="U141" s="6"/>
-      <c r="V141" s="6"/>
-      <c r="W141" s="6"/>
-      <c r="X141" s="8"/>
-      <c r="Y141" s="6"/>
-      <c r="Z141" s="6"/>
-      <c r="AA141" s="8"/>
-      <c r="AB141" s="8"/>
-      <c r="AC141" s="8"/>
-      <c r="AD141" s="8"/>
-      <c r="AE141" s="6"/>
+      <c r="O141" s="5">
+        <v>1089.1600000000001</v>
+      </c>
+      <c r="P141" s="5">
+        <v>1089.1600000000001</v>
+      </c>
+      <c r="Q141" s="6">
+        <v>0.19859139429954875</v>
+      </c>
+      <c r="R141" s="7">
+        <v>17</v>
+      </c>
+      <c r="S141" s="6">
+        <v>0.30769230769230771</v>
+      </c>
+      <c r="T141" s="6">
+        <v>0.32378860773440082</v>
+      </c>
+      <c r="U141" s="6">
+        <v>0.0049190201623269302</v>
+      </c>
+      <c r="V141" s="6">
+        <v>0.35765498182085276</v>
+      </c>
+      <c r="W141" s="6">
+        <v>0.17422922252010722</v>
+      </c>
+      <c r="X141" s="8">
+        <v>17.445235714285715</v>
+      </c>
+      <c r="Y141" s="6">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="Z141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA141" s="8">
+        <v>2.2607823529411766</v>
+      </c>
+      <c r="AB141" s="8">
+        <v>2.0714285714285716</v>
+      </c>
+      <c r="AC141" s="8">
+        <v>4.5023799999999996</v>
+      </c>
+      <c r="AD141" s="8">
+        <v>12.440478571428571</v>
+      </c>
+      <c r="AE141" s="6">
+        <v>1</v>
+      </c>
       <c r="AF141" s="9"/>
-      <c r="AG141" s="5"/>
+      <c r="AG141" s="5">
+        <v>0</v>
+      </c>
       <c r="AH141" s="10">
         <v>4</v>
       </c>
@@ -26134,7 +26175,9 @@
       <c r="AB195" s="8">
         <v>4.2666666666666666</v>
       </c>
-      <c r="AC195" s="8"/>
+      <c r="AC195" s="8">
+        <v>8.4342579999999998</v>
+      </c>
       <c r="AD195" s="8">
         <v>15.332405555555555</v>
       </c>
@@ -28468,112 +28511,203 @@
         <v>56</v>
       </c>
     </row>
-    <row r="216" ht="24.75" customHeight="1">
-      <c t="s" r="A216" s="14">
+    <row r="216" ht="13.5" customHeight="1">
+      <c r="A216" s="2">
+        <v>19980</v>
+      </c>
+      <c r="B216" s="3">
+        <v>-1</v>
+      </c>
+      <c t="s" r="C216" s="4">
+        <v>44</v>
+      </c>
+      <c t="s" r="D216" s="4">
+        <v>45</v>
+      </c>
+      <c t="s" r="E216" s="4">
+        <v>46</v>
+      </c>
+      <c t="s" r="F216" s="4">
+        <v>47</v>
+      </c>
+      <c t="s" r="G216" s="4">
+        <v>48</v>
+      </c>
+      <c t="s" r="H216" s="4">
+        <v>49</v>
+      </c>
+      <c t="s" r="I216" s="4">
+        <v>50</v>
+      </c>
+      <c t="s" r="J216" s="4">
+        <v>47</v>
+      </c>
+      <c t="s" r="K216" s="4">
+        <v>51</v>
+      </c>
+      <c t="s" r="L216" s="4">
+        <v>51</v>
+      </c>
+      <c r="M216" s="4"/>
+      <c t="s" r="N216" s="4">
+        <v>52</v>
+      </c>
+      <c r="O216" s="5"/>
+      <c r="P216" s="5"/>
+      <c r="Q216" s="6"/>
+      <c r="R216" s="7"/>
+      <c r="S216" s="6"/>
+      <c r="T216" s="6"/>
+      <c r="U216" s="6"/>
+      <c r="V216" s="6"/>
+      <c r="W216" s="6"/>
+      <c r="X216" s="8"/>
+      <c r="Y216" s="6"/>
+      <c r="Z216" s="6"/>
+      <c r="AA216" s="8"/>
+      <c r="AB216" s="8"/>
+      <c r="AC216" s="8"/>
+      <c r="AD216" s="8"/>
+      <c r="AE216" s="6"/>
+      <c r="AF216" s="9"/>
+      <c r="AG216" s="5"/>
+      <c r="AH216" s="10"/>
+      <c r="AI216" s="11"/>
+      <c r="AJ216" s="12"/>
+      <c t="s" r="AK216" s="4">
+        <v>52</v>
+      </c>
+      <c t="s" r="AL216" s="4">
+        <v>52</v>
+      </c>
+      <c r="AM216" s="2">
+        <v>1</v>
+      </c>
+      <c r="AN216" s="2">
+        <v>1</v>
+      </c>
+      <c t="s" r="AO216" s="4">
+        <v>53</v>
+      </c>
+      <c t="s" r="AP216" s="4">
+        <v>54</v>
+      </c>
+      <c t="s" r="AQ216" s="4">
+        <v>55</v>
+      </c>
+      <c t="s" r="AR216" s="4">
         <v>300</v>
       </c>
-      <c t="s" r="B216" s="14">
+      <c t="s" r="AS216" s="4">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="217" ht="24.75" customHeight="1">
+      <c t="s" r="A217" s="14">
         <v>301</v>
       </c>
-      <c r="C216" s="15"/>
-      <c r="D216" s="15"/>
-      <c r="E216" s="15"/>
-      <c r="F216" s="15"/>
-      <c r="G216" s="15"/>
-      <c r="H216" s="15"/>
-      <c r="I216" s="15"/>
-      <c r="J216" s="15"/>
-      <c r="K216" s="15"/>
-      <c r="L216" s="15"/>
-      <c r="M216" s="15"/>
-      <c t="s" r="N216" s="15">
-        <v>52</v>
-      </c>
-      <c t="s" r="O216" s="14">
+      <c t="s" r="B217" s="14">
         <v>302</v>
       </c>
-      <c t="s" r="P216" s="14">
+      <c r="C217" s="15"/>
+      <c r="D217" s="15"/>
+      <c r="E217" s="15"/>
+      <c r="F217" s="15"/>
+      <c r="G217" s="15"/>
+      <c r="H217" s="15"/>
+      <c r="I217" s="15"/>
+      <c r="J217" s="15"/>
+      <c r="K217" s="15"/>
+      <c r="L217" s="15"/>
+      <c r="M217" s="15"/>
+      <c t="s" r="N217" s="15">
+        <v>52</v>
+      </c>
+      <c t="s" r="O217" s="14">
         <v>303</v>
       </c>
-      <c t="s" r="Q216" s="14">
+      <c t="s" r="P217" s="14">
         <v>304</v>
       </c>
-      <c t="s" r="R216" s="14">
+      <c t="s" r="Q217" s="14">
         <v>305</v>
       </c>
-      <c t="s" r="S216" s="14">
+      <c t="s" r="R217" s="14">
         <v>306</v>
       </c>
-      <c t="s" r="T216" s="14">
+      <c t="s" r="S217" s="14">
         <v>307</v>
       </c>
-      <c t="s" r="U216" s="14">
+      <c t="s" r="T217" s="14">
         <v>308</v>
       </c>
-      <c t="s" r="V216" s="14">
-        <v>307</v>
-      </c>
-      <c t="s" r="W216" s="14">
+      <c t="s" r="U217" s="14">
         <v>309</v>
       </c>
-      <c t="s" r="X216" s="14">
+      <c t="s" r="V217" s="14">
+        <v>308</v>
+      </c>
+      <c t="s" r="W217" s="14">
         <v>310</v>
       </c>
-      <c t="s" r="Y216" s="14">
+      <c t="s" r="X217" s="14">
         <v>311</v>
       </c>
-      <c t="s" r="Z216" s="14">
+      <c t="s" r="Y217" s="14">
         <v>312</v>
       </c>
-      <c t="s" r="AA216" s="14">
+      <c t="s" r="Z217" s="14">
         <v>313</v>
       </c>
-      <c t="s" r="AB216" s="14">
+      <c t="s" r="AA217" s="14">
         <v>314</v>
       </c>
-      <c t="s" r="AC216" s="14">
+      <c t="s" r="AB217" s="14">
         <v>315</v>
       </c>
-      <c t="s" r="AD216" s="14">
+      <c t="s" r="AC217" s="14">
         <v>316</v>
       </c>
-      <c t="s" r="AE216" s="14">
+      <c t="s" r="AD217" s="14">
         <v>317</v>
       </c>
-      <c r="AF216" s="14"/>
-      <c t="s" r="AG216" s="14">
+      <c t="s" r="AE217" s="14">
         <v>318</v>
       </c>
-      <c t="s" r="AH216" s="14">
+      <c r="AF217" s="14"/>
+      <c t="s" r="AG217" s="14">
         <v>319</v>
       </c>
-      <c t="s" r="AI216" s="14">
+      <c t="s" r="AH217" s="14">
         <v>320</v>
       </c>
-      <c r="AJ216" s="15"/>
-      <c t="s" r="AK216" s="15">
-        <v>52</v>
-      </c>
-      <c t="s" r="AL216" s="15">
-        <v>52</v>
-      </c>
-      <c t="s" r="AM216" s="14">
+      <c t="s" r="AI217" s="14">
         <v>321</v>
       </c>
-      <c t="s" r="AN216" s="14">
-        <v>321</v>
-      </c>
-      <c r="AO216" s="15"/>
-      <c r="AP216" s="15"/>
-      <c r="AQ216" s="15"/>
-      <c r="AR216" s="15"/>
-      <c r="AS216" s="15"/>
+      <c r="AJ217" s="15"/>
+      <c t="s" r="AK217" s="15">
+        <v>52</v>
+      </c>
+      <c t="s" r="AL217" s="15">
+        <v>52</v>
+      </c>
+      <c t="s" r="AM217" s="14">
+        <v>322</v>
+      </c>
+      <c t="s" r="AN217" s="14">
+        <v>322</v>
+      </c>
+      <c r="AO217" s="15"/>
+      <c r="AP217" s="15"/>
+      <c r="AQ217" s="15"/>
+      <c r="AR217" s="15"/>
+      <c r="AS217" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:AS216" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:AS217" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>